--- a/LubanConfig/MiniTemplate/Datas/生成数据/#肉鸽技能选择节奏_1导.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/生成数据/#肉鸽技能选择节奏_1导.xlsx
@@ -79,24 +79,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -112,7 +114,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -129,20 +138,20 @@
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1527,8 +1536,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>